--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104661_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104661_W23.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9487</v>
+        <v>5.4257</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2496</v>
+        <v>5.7147</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3008</v>
+        <v>-0.2891</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2234</v>
+        <v>1.2198</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.0445</v>
+        <v>-2.0531</v>
       </c>
       <c r="I2" t="n">
-        <v>3.268</v>
+        <v>3.2729</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8049</v>
+        <v>2.7664</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0284</v>
+        <v>-0.0559</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8334</v>
+        <v>2.8223</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5815</v>
+        <v>-1.5466</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0161</v>
+        <v>-1.9971</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0055</v>
+        <v>1.4807</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4861</v>
+        <v>1.997</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4806</v>
+        <v>-0.5163</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8124</v>
+        <v>1.8146</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1734</v>
+        <v>0.1804</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1291</v>
+        <v>3.1943</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8921</v>
+        <v>3.844</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.763</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9656</v>
+        <v>1.9597</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1211</v>
+        <v>-1.1283</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0867</v>
+        <v>3.088</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7882</v>
+        <v>2.7619</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1598</v>
+        <v>-0.1798</v>
       </c>
       <c r="L3" t="n">
-        <v>2.948</v>
+        <v>2.9417</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8225</v>
+        <v>-0.8022</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.483</v>
+        <v>0.5517</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1039</v>
+        <v>1.0821</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6209</v>
+        <v>-0.5304</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0168</v>
+        <v>0.8626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3082</v>
+        <v>0.7831</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2914</v>
+        <v>0.0795</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2546</v>
+        <v>1.2608</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.622</v>
+        <v>-0.6177</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8765</v>
+        <v>1.8785</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8053</v>
+        <v>1.7891</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5507</v>
+        <v>-0.5284</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3965</v>
+        <v>0.4425</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3176</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7141</v>
+        <v>-0.3725</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06320000000000001</v>
+        <v>0.4847</v>
       </c>
       <c r="E5" t="n">
-        <v>1.713</v>
+        <v>2.4742</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7762</v>
+        <v>-1.9895</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1844</v>
+        <v>-1.1797</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.893</v>
+        <v>-2.8977</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7087</v>
+        <v>1.7179</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5067</v>
+        <v>0.4814</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3964</v>
+        <v>-1.4176</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6911</v>
+        <v>-1.6612</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1627</v>
+        <v>0.7131</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0302</v>
+        <v>0.7731</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1929</v>
+        <v>-0.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3572</v>
+        <v>-0.0399</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9361</v>
+        <v>-0.4863</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5789</v>
+        <v>0.4464</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3812</v>
+        <v>0.3807</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8397</v>
+        <v>0.8441</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4585</v>
+        <v>-0.4635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.927</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0081</v>
+        <v>-0.023</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5458</v>
+        <v>-0.5271</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2616</v>
+        <v>0.5794</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0484</v>
+        <v>0.427</v>
       </c>
       <c r="U6" t="n">
-        <v>0.31</v>
+        <v>0.1524</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7783</v>
+        <v>-0.9915</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7373</v>
+        <v>-1.8744</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9591</v>
+        <v>0.8829</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0517</v>
+        <v>-2.0615</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7041</v>
+        <v>1.7032</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.7558</v>
+        <v>-3.7647</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6708</v>
+        <v>-1.6907</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.1081</v>
+        <v>-3.1213</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3808</v>
+        <v>-0.3708</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2669</v>
+        <v>0.2725</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.636</v>
+        <v>0.4261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1603</v>
+        <v>0.0439</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4757</v>
+        <v>0.3823</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.27</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.855</v>
+        <v>-1.0829</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.784</v>
+        <v>-2.127</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0711</v>
+        <v>1.0442</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5912</v>
+        <v>-1.7889</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5699</v>
+        <v>-1.4987</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0213</v>
+        <v>-0.2902</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5008</v>
+        <v>-1.4181</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5381</v>
+        <v>-1.4554</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.3708</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0318</v>
+        <v>-0.0433</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0586</v>
+        <v>-0.3275</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5093</v>
+        <v>0.706</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7168</v>
+        <v>0.2715</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2075</v>
+        <v>0.4345</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9011</v>
+        <v>-1.0982</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9903</v>
+        <v>-0.9061</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0892</v>
+        <v>-0.1921</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7848</v>
+        <v>-1.593</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.489</v>
+        <v>-1.5737</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2958</v>
+        <v>-0.0193</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.404</v>
+        <v>-1.5076</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4413</v>
+        <v>-1.5448</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3808</v>
+        <v>-0.0854</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0477</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3331</v>
+        <v>-0.0565</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8837</v>
+        <v>0.2671</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3871</v>
+        <v>0.6015</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4966</v>
+        <v>-0.3344</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9433</v>
+        <v>-3.5956</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8057</v>
+        <v>-0.2821</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1376</v>
+        <v>-3.3136</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9032</v>
+        <v>-4.6161</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6189</v>
+        <v>-2.0391</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2843</v>
+        <v>-2.577</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2916</v>
+        <v>-2.3813</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1692</v>
+        <v>-0.042</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4608</v>
+        <v>-2.3394</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6116</v>
+        <v>-2.2348</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.788</v>
+        <v>-1.9971</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8236</v>
+        <v>-0.2377</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0415</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-2.9592</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>3.094</v>
+        <v>0.8024</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1152</v>
+        <v>1.4745</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0212</v>
+        <v>-0.672</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>1.3562</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.584</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-2.2278</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0586</v>
+        <v>-4.6129</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2028</v>
+        <v>-4.6578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1441</v>
+        <v>0.045</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7832</v>
+        <v>-3.8001</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0776</v>
+        <v>-1.0934</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7055</v>
+        <v>-2.7067</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.896</v>
+        <v>-2.9295</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1713</v>
+        <v>-1.1936</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8871</v>
+        <v>-0.8706</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0321</v>
+        <v>0.4343</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6775</v>
+        <v>-0.0863</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6454</v>
+        <v>0.5206</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2645</v>
+        <v>-4.6467</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4985</v>
+        <v>-3.5387</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7659</v>
+        <v>-1.1079</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.615</v>
+        <v>-2.9089</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0374</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5776</v>
+        <v>-2.2804</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3458</v>
+        <v>-1.3199</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0213</v>
+        <v>0.1477</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3245</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2692</v>
+        <v>-1.589</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0161</v>
+        <v>-0.7761</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2531</v>
+        <v>-0.8129</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9488</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.878</v>
+        <v>1.4004</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1966</v>
+        <v>1.4233</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0746</v>
+        <v>-0.0229</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3627</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>3.5994</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2368</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.126600000000001</v>
+        <v>-6.100399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.791799999999999</v>
+        <v>-1.056399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.3347</v>
+        <v>-5.043900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.0887</v>
+        <v>-13.1272</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.9296</v>
+        <v>-10.9829</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1589</v>
+        <v>-2.1445</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.276900000000001</v>
+        <v>-2.540500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.0489</v>
+        <v>-3.2215</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7721999999999989</v>
+        <v>0.6810999999999985</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.8115</v>
+        <v>-10.5869</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.8803</v>
+        <v>-7.761000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.9312</v>
+        <v>-2.8257</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4027</v>
+        <v>-3.4147</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>6.729200000000001</v>
+        <v>7.8037</v>
       </c>
       <c r="T13" t="n">
-        <v>7.727499999999999</v>
+        <v>8.822600000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9982999999999999</v>
+        <v>-1.0187</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6351</v>
+        <v>2.6374</v>
       </c>
       <c r="W13" t="n">
-        <v>9.7698</v>
+        <v>9.7339</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1347</v>
+        <v>-7.0965</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9306</v>
+        <v>3.6939</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3591</v>
+        <v>0.6767</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4286</v>
+        <v>3.0172</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9783</v>
+        <v>4.8572</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6824</v>
+        <v>0.2129</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2959</v>
+        <v>4.6443</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5099</v>
+        <v>3.6352</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7636</v>
+        <v>-0.0732</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7463</v>
+        <v>3.7083</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5316</v>
+        <v>1.222</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.2861</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4504</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4286</v>
+        <v>-0.2543</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5939</v>
+        <v>0.1389</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1653</v>
+        <v>-0.3932</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6105</v>
+        <v>0.2292</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4822</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5094</v>
+        <v>3.4593</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1435</v>
+        <v>2.0646</v>
       </c>
       <c r="F15" t="n">
-        <v>1.366</v>
+        <v>1.3947</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4263</v>
+        <v>2.4294</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5165</v>
+        <v>3.5182</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0902</v>
+        <v>-1.0888</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5906</v>
+        <v>2.5681</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8573</v>
+        <v>2.8441</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1644</v>
+        <v>-0.1387</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3459</v>
+        <v>-0.4041</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>0.1111</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5111</v>
+        <v>-0.5152</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.348</v>
+        <v>2.8531</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4695</v>
+        <v>4.152</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1215</v>
+        <v>-1.299</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3577</v>
+        <v>2.9895</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5079</v>
+        <v>2.6852</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8498</v>
+        <v>0.3043</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4684</v>
+        <v>3.4887</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3841</v>
+        <v>2.7439</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0843</v>
+        <v>0.7447</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1107</v>
+        <v>-0.4992</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1238</v>
+        <v>-0.0587</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.4405</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6293</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4174</v>
+        <v>-0.6584</v>
       </c>
       <c r="T16" t="n">
-        <v>0.738</v>
+        <v>0.4177</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3206</v>
+        <v>-1.0761</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>-0.6162</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8924</v>
+        <v>0.4733</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9324</v>
+        <v>1.6177</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4459</v>
+        <v>1.0066</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3782</v>
+        <v>0.6111</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8707</v>
+        <v>1.6606</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2194</v>
+        <v>0.4165</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6513</v>
+        <v>1.2442</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6805</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0457</v>
+        <v>-0.1142</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7263</v>
+        <v>0.782</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1902</v>
+        <v>0.9928</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2652</v>
+        <v>0.5306</v>
       </c>
       <c r="O17" t="n">
-        <v>0.925</v>
+        <v>0.4622</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0291</v>
+        <v>0.2451</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0434</v>
+        <v>0.3388</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9857</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2249</v>
+        <v>-2.3367</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8462</v>
+        <v>1.3526</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4904</v>
+        <v>1.5915</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3558</v>
+        <v>-0.2388</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6539</v>
+        <v>2.3549</v>
       </c>
       <c r="H18" t="n">
-        <v>0.417</v>
+        <v>0.5111</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2369</v>
+        <v>1.8439</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6829</v>
+        <v>2.4384</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1008</v>
+        <v>0.3685</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7837</v>
+        <v>2.0699</v>
       </c>
       <c r="M18" t="n">
-        <v>0.971</v>
+        <v>-0.0835</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5178</v>
+        <v>0.1426</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0415</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4969</v>
+        <v>-0.5666</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8075</v>
+        <v>-0.0863</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3106</v>
+        <v>-0.4804</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3461</v>
+        <v>0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.8814</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3461</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2905</v>
+        <v>0.3255</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2159</v>
+        <v>0.251</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6773</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6082</v>
+        <v>-0.5794</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6082</v>
+        <v>-0.5794</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4793</v>
+        <v>1.6835</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0131</v>
+        <v>-1.7585</v>
       </c>
       <c r="G20" t="n">
-        <v>2.863</v>
+        <v>2.8668</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1354</v>
+        <v>2.1476</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7276</v>
+        <v>0.7191</v>
       </c>
       <c r="J20" t="n">
-        <v>2.286</v>
+        <v>2.262</v>
       </c>
       <c r="K20" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M20" t="n">
-        <v>0.577</v>
+        <v>0.6048</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4383</v>
+        <v>0.4584</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7578</v>
+        <v>-1.3075</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9926</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9906</v>
+        <v>-0.8223</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0918</v>
+        <v>-1.0961</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1011</v>
+        <v>0.2738</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.042</v>
+        <v>-0.0314</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2612</v>
+        <v>-0.2607</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6324</v>
+        <v>0.6465</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8559</v>
+        <v>-0.7014</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4386</v>
+        <v>-0.2832</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9077</v>
+        <v>-1.2654</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9415</v>
+        <v>-1.6511</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0338</v>
+        <v>0.3857</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6736</v>
+        <v>-2.0021</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8556</v>
+        <v>-0.1994</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.5292</v>
+        <v>-1.8027</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0138</v>
+        <v>-1.8204</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5746</v>
+        <v>-0.2553</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.5884</v>
+        <v>-1.5651</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6597</v>
+        <v>-0.1817</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2811</v>
+        <v>0.0559</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9408</v>
+        <v>-0.2377</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>2.722</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>0.764</v>
+        <v>-1.2147</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2461</v>
+        <v>0.2666</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4821</v>
+        <v>-1.4813</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2249</v>
+        <v>2.1789</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3214</v>
+        <v>2.1789</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2985</v>
+        <v>-2.4141</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2027</v>
+        <v>-3.4581</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0959</v>
+        <v>1.0441</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0177</v>
+        <v>-2.675</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2211</v>
+        <v>0.8586</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7966</v>
+        <v>-3.5336</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7931</v>
+        <v>-2.0496</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2495</v>
+        <v>0.5581</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5435</v>
+        <v>-2.6077</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2247</v>
+        <v>-0.6254</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0284</v>
+        <v>0.3005</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2531</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2393</v>
+        <v>0.2625</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3266</v>
+        <v>0.7799</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.9127</v>
+        <v>-0.5174</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1853</v>
+        <v>-0.2292</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1853</v>
+        <v>0.3155</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.126499999999998</v>
+        <v>8.725299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>5.3345</v>
+        <v>5.0441</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7917</v>
+        <v>3.6813</v>
       </c>
       <c r="G24" t="n">
-        <v>13.0885</v>
+        <v>13.1272</v>
       </c>
       <c r="H24" t="n">
-        <v>10.9296</v>
+        <v>10.9827</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1589</v>
+        <v>2.144500000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>10.8116</v>
+        <v>10.5868</v>
       </c>
       <c r="K24" t="n">
-        <v>7.8806</v>
+        <v>7.761100000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>2.9312</v>
+        <v>2.825499999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>2.2768</v>
+        <v>2.5404</v>
       </c>
       <c r="N24" t="n">
-        <v>3.0491</v>
+        <v>3.2215</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7722999999999998</v>
+        <v>-0.6811999999999998</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.6099</v>
+        <v>-13.6578</v>
       </c>
       <c r="R24" t="n">
-        <v>17.0126</v>
+        <v>17.0724</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.7293</v>
+        <v>-5.1788</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9982000000000002</v>
+        <v>1.0187</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.727500000000001</v>
+        <v>-6.1976</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.6351</v>
+        <v>-2.6374</v>
       </c>
       <c r="W24" t="n">
-        <v>7.1347</v>
+        <v>7.096300000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.769800000000002</v>
+        <v>-9.733700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104661_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104661_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.1804</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.2278</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.0965</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104661_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.733700000000001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
